--- a/important_mails_2026-04-18.xlsx
+++ b/important_mails_2026-04-18.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,68 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
+          <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Create FBA removal order by 2026-04-30</t>
+          <t>Pagamento elaborato con successo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 04/18/26 15:14 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 202,18.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -536,39 +583,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -591,39 +638,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -632,39 +679,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -684,39 +731,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -733,39 +780,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -777,39 +824,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -829,62 +876,6 @@
  Luxembourg VAT Reg. No. LU 20260743.
  This email is sent from an unmonitored email address.
  SPC-EUAmazon-439806292595808</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Rettifica del saldo negativo nei tuoi account</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Abbiamo rettificato il tuo saldo negativo di 285.13 € dovuto dal tuo account venditore Amazon.it in data aprile 11, 2026, utilizzando i fondi disponibili nei tuoi account Amazon.fr, Amazon.es. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
-Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
-Distinti saluti,
-Amazon Payments Europe
- Segnala un problema con questa e-mail
- Per qualsiasi domanda consulta: Seller Central
- Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
- Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
- Amazon Payments Europe
- 38 avenue John F. Kennedy,
- L-1855 Lussemburgo,
- Numero di registrazione in Lussemburgo: B-101818,
- Capitale Sociale 165.833 EUR,
- Numero di licenza di attività commerciale: 134248,
- Partita IVA n. LU 20260743.
- Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
- SPC-EUAmazon-1301823410754995</t>
         </is>
       </c>
     </row>
@@ -2037,21 +2028,77 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
+          <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Balance Paid on Your Selling on Amazon payment account</t>
+          <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Abbiamo rettificato il tuo saldo negativo di 285.13 € dovuto dal tuo account venditore Amazon.it in data aprile 11, 2026, utilizzando i fondi disponibili nei tuoi account Amazon.fr, Amazon.es. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
+Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
+Distinti saluti,
+Amazon Payments Europe
+ Segnala un problema con questa e-mail
+ Per qualsiasi domanda consulta: Seller Central
+ Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
+ Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Lussemburgo,
+ Numero di registrazione in Lussemburgo: B-101818,
+ Capitale Sociale 165.833 EUR,
+ Numero di licenza di attività commerciale: 134248,
+ Partita IVA n. LU 20260743.
+ Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
+ SPC-EUAmazon-1301823410754995</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Balance Paid on Your Selling on Amazon payment account</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -2066,39 +2113,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2112,40 +2159,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2162,39 +2209,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2214,39 +2261,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2263,39 +2310,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2318,39 +2365,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2370,39 +2417,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2416,55 +2463,6 @@
 Note: Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
  We’ll continue to provide you with quarterly updates on data shared with the Chinese tax authority.
  For more information, go to China tax information reporti</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 03/19/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 74,59.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxit</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6478,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6495,168 +6493,21 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
+          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Seller News: March 2026</t>
+          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services
- 96
- Updates to Seller Central workspaces, Upload Images, Product Opportunity explorer, and more.
- Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
- Introducing a new, AI-powered workspace
- You now have access to a dynamic canvas experience in Seller Central, where you can visualize data and key insights, explore scenarios, and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalized and actionable insights. Read more .
- Upload Images now provides faster uploads and more flexibility
- We’ve enhanced the image upload process in Upload Images to make managing images for your product catalog faster and more flexible. Read more .
- Remove meltable FBA inventory by April 20
- To meet product quality standards, we won’t accept meltable inventory at our fulfillment centers between April 20, 2026, and September 28, 2026. Meltable inventory remaining in our fulfillment centers after April 20, may be marked unfillable and disposed of for a fee, starting May 1, 2026. Read more .
- Save and track pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Act today &amp; improve Sales on Excess Inventory</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Optional preview text
- Hello,
-We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
-X004QEYPRL, X004QFJQLF, X004MMFUYT, X004QEVV05, X004K6ILMZ
-We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
- Outlet deals
- Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
- Create Outlet Deal Today!
- Sponsored Product Ads
- Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
- Create Sponsored Products Ad Today!</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: March 2026</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services
- 96
- Stay informed about selling on Amazon.
- Our Seller Newsletter provides the most important policy, tool and programme updates from the past month.
- Introducing a new, AI-powered workspace
- You now have access to a dynamic canvas experience in Seller Central, where you can visualise data and key insights, explore scenarios and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalised and actionable insights. Read more .
- Upload Images now provides faster uploads and more flexibility
- We’ve enhanced the image upload process in Upload Images to make managing images for your product catalogue faster and more flexible. Read more .
- Save and track product research with Product Opportunity Explorer
- Product Opportunity Explorer now includes a feature that helps you save and organise your research. You can identify profitable opportunities with low competition and save those promising product niches and ASINs with a single click. Read more .
- Account health tips for multiple selling accounts
- Our multiple-accounts policy allows you to operate one account per region unless you have a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6669,39 +6520,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6722,39 +6573,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6777,39 +6628,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6830,39 +6681,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6886,39 +6737,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6941,39 +6792,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -6989,39 +6840,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7041,39 +6892,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7092,39 +6943,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7133,39 +6984,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7183,39 +7034,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7245,39 +7096,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7293,39 +7144,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
